--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486701_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486701_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0306</v>
+        <v>1.3523</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3423</v>
+        <v>1.6391</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3117</v>
+        <v>-0.2869</v>
       </c>
       <c r="G2" t="n">
         <v>0.7685999999999999</v>
@@ -610,13 +610,13 @@
         <v>2.1239</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6455</v>
+        <v>-1.3238</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6612</v>
+        <v>-0.0419</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.3067</v>
+        <v>-1.2819</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. ALONSO LANTIGUA</t>
+          <t>A. CHACON GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1491</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1651</v>
+        <v>-0.4297</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.016</v>
+        <v>1.3304</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3367</v>
+        <v>-0.2025</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9037</v>
+        <v>-0.0556</v>
       </c>
       <c r="I3" t="n">
-        <v>2.2404</v>
+        <v>-0.1469</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2757</v>
+        <v>-0.4846</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.2134</v>
+        <v>0.0828</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4891</v>
+        <v>-0.5674</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9389999999999999</v>
+        <v>0.2821</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6903</v>
+        <v>-0.1384</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2487</v>
+        <v>0.4205</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5792</v>
+        <v>1.3515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1931</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7723</v>
+        <v>1.3515</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7669</v>
+        <v>-0.2483</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0825</v>
+        <v>0.0549</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.3032</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. CHACON GARCIA</t>
+          <t>A. ALONSO LANTIGUA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1229</v>
+        <v>0.5161</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0089</v>
+        <v>1.2341</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1318</v>
+        <v>-0.718</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.2025</v>
+        <v>0.3367</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0556</v>
+        <v>-1.9037</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1469</v>
+        <v>2.2404</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4846</v>
+        <v>1.2757</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0828</v>
+        <v>-1.2134</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5674</v>
+        <v>2.4891</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2821</v>
+        <v>-0.9389999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1384</v>
+        <v>-0.6903</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4205</v>
+        <v>-0.2487</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3515</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.1931</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3515</v>
+        <v>0.7723</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0261</v>
+        <v>-0.3998</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5243</v>
+        <v>0.1515</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5019</v>
+        <v>-0.5513</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. PEREZ CHAFINO</t>
+          <t>G. GUERRA LOZANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0143</v>
+        <v>0.4133</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4993</v>
+        <v>0.5858</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5135999999999999</v>
+        <v>-0.1725</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4796</v>
+        <v>1.7635</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9309</v>
+        <v>0.9452</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4513</v>
+        <v>0.8183</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.5059</v>
+        <v>2.2758</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.2406</v>
+        <v>2.1875</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7347</v>
+        <v>0.0882</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0263</v>
+        <v>-0.5122</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6903</v>
+        <v>-1.2423</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7165</v>
+        <v>0.7301</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3515</v>
+        <v>0.9654</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3515</v>
+        <v>2.1239</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7997</v>
+        <v>-1.7443</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2211</v>
+        <v>-0.5315</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5786</v>
+        <v>-1.2129</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9421</v>
+        <v>-0.5712</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. GUERRA LOZANO</t>
+          <t>A. PEREZ GALVAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3962</v>
+        <v>-0.2135</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3727</v>
+        <v>0.5323</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0235</v>
+        <v>-0.7459</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7635</v>
+        <v>1.2001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9452</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8183</v>
+        <v>0.4476</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2758</v>
+        <v>1.1051</v>
       </c>
       <c r="K6" t="n">
-        <v>2.1875</v>
+        <v>1.7877</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0882</v>
+        <v>-0.6826</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5122</v>
+        <v>0.095</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2423</v>
+        <v>-1.0352</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7301</v>
+        <v>1.1302</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9654</v>
+        <v>2.1239</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>2.1239</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.5539</v>
+        <v>-2.3098</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.49</v>
+        <v>-0.5728</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0639</v>
+        <v>-1.737</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PEREZ GALVAN</t>
+          <t>M. PEREZ CHAFINO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7501</v>
+        <v>-0.3166</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0538</v>
+        <v>-0.5819</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6962</v>
+        <v>0.2653</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2001</v>
+        <v>-1.4796</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7524999999999999</v>
+        <v>-2.9309</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4476</v>
+        <v>1.4513</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1051</v>
+        <v>-1.5059</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7877</v>
+        <v>-2.2406</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6826</v>
+        <v>0.7347</v>
       </c>
       <c r="M7" t="n">
-        <v>0.095</v>
+        <v>0.0263</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0352</v>
+        <v>-0.6903</v>
       </c>
       <c r="O7" t="n">
-        <v>1.1302</v>
+        <v>0.7165</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1239</v>
+        <v>1.3515</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.8463</v>
+        <v>-1.1306</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.1589</v>
+        <v>-0.3037</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.6874</v>
+        <v>-0.827</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.2277</v>
+        <v>0.9421</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2277</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4505</v>
+        <v>-1.4215</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3096</v>
+        <v>0.413</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7601</v>
+        <v>-1.8346</v>
       </c>
       <c r="G8" t="n">
         <v>0.3233</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5461</v>
+        <v>-0.5171</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0828</v>
+        <v>0.0206</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4632</v>
+        <v>-0.5377</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2277</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9326</v>
+        <v>-1.8057</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8431999999999999</v>
+        <v>-0.5673</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0894</v>
+        <v>-1.2384</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5825</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4506</v>
+        <v>-1.3237</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4418</v>
+        <v>-0.1659</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0088</v>
+        <v>-1.1578</v>
       </c>
       <c r="V9" t="n">
         <v>-0.2856</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5607</v>
+        <v>-3.9911</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.161</v>
+        <v>-1.7403</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.3998</v>
+        <v>-2.2508</v>
       </c>
       <c r="G10" t="n">
         <v>1.5958</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>-3.0173</v>
+        <v>-2.4477</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9657</v>
+        <v>-0.5451</v>
       </c>
       <c r="U10" t="n">
-        <v>-2.0516</v>
+        <v>-1.9026</v>
       </c>
       <c r="V10" t="n">
         <v>-0.243</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.773199999999999</v>
+        <v>-4.565999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1219</v>
+        <v>1.0851</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.6513</v>
+        <v>-5.6514</v>
       </c>
       <c r="G11" t="n">
         <v>3.7234</v>
@@ -1282,7 +1282,7 @@
         <v>-5.1722</v>
       </c>
       <c r="I11" t="n">
-        <v>8.895600000000002</v>
+        <v>8.8956</v>
       </c>
       <c r="J11" t="n">
         <v>8.286899999999999</v>
@@ -1312,10 +1312,10 @@
         <v>12.5501</v>
       </c>
       <c r="S11" t="n">
-        <v>-13.6524</v>
+        <v>-11.4451</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.1409</v>
+        <v>-1.9339</v>
       </c>
       <c r="U11" t="n">
         <v>-9.5114</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>D. SANCHEZ PEREZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.2435</v>
+        <v>4.9883</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4498</v>
+        <v>4.9342</v>
       </c>
       <c r="F12" t="n">
-        <v>1.7937</v>
+        <v>0.0541</v>
       </c>
       <c r="G12" t="n">
-        <v>3.212</v>
+        <v>3.5143</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6966</v>
+        <v>2.5173</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5154</v>
+        <v>0.9969</v>
       </c>
       <c r="J12" t="n">
-        <v>1.9511</v>
+        <v>3.6257</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8697</v>
+        <v>2.2422</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0814</v>
+        <v>1.3835</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2609</v>
+        <v>-0.1115</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8269</v>
+        <v>0.2752</v>
       </c>
       <c r="O12" t="n">
-        <v>0.434</v>
+        <v>-0.3866</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5792</v>
+        <v>0.9654</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3597</v>
+        <v>1.779</v>
       </c>
       <c r="T12" t="n">
-        <v>2.1784</v>
+        <v>1.3511</v>
       </c>
       <c r="U12" t="n">
-        <v>1.1813</v>
+        <v>0.4279</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9421</v>
+        <v>-1.2703</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2856</v>
+        <v>-0.0426</v>
       </c>
       <c r="X12" t="n">
         <v>-1.2277</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. SANCHEZ PEREZ</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.4119</v>
+        <v>4.1456</v>
       </c>
       <c r="E13" t="n">
-        <v>4.5205</v>
+        <v>2.6224</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1086</v>
+        <v>1.5232</v>
       </c>
       <c r="G13" t="n">
-        <v>3.5143</v>
+        <v>3.212</v>
       </c>
       <c r="H13" t="n">
-        <v>2.5173</v>
+        <v>2.6966</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9969</v>
+        <v>0.5154</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6257</v>
+        <v>1.9511</v>
       </c>
       <c r="K13" t="n">
-        <v>2.2422</v>
+        <v>1.8697</v>
       </c>
       <c r="L13" t="n">
-        <v>1.3835</v>
+        <v>0.0814</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1115</v>
+        <v>1.2609</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2752</v>
+        <v>0.8269</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3866</v>
+        <v>0.434</v>
       </c>
       <c r="P13" t="n">
-        <v>0.9654</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2026</v>
+        <v>2.2618</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9374</v>
+        <v>1.3511</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2652</v>
+        <v>0.9107</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.2703</v>
+        <v>-0.9421</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.0426</v>
+        <v>0.2856</v>
       </c>
       <c r="X13" t="n">
         <v>-1.2277</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. DIAZ MARTINEZ</t>
+          <t>M. LAGUNA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4709</v>
+        <v>2.3656</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3863</v>
+        <v>1.9802</v>
       </c>
       <c r="F14" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.3854</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.4583</v>
+        <v>0.6211</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0411</v>
+        <v>0.924</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.4994</v>
+        <v>-0.303</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0187</v>
+        <v>1.422</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0419</v>
+        <v>1.3384</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.0232</v>
+        <v>0.0837</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.477</v>
+        <v>-0.8008999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.0008</v>
+        <v>-0.4143</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.4763</v>
+        <v>-0.3866</v>
       </c>
       <c r="P14" t="n">
-        <v>-2.1239</v>
+        <v>0.5792</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.7723</v>
+        <v>0.5792</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5398</v>
+        <v>1.1653</v>
       </c>
       <c r="T14" t="n">
-        <v>3.7505</v>
+        <v>0.5582</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7893</v>
+        <v>0.6071</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. LAGUNA RODRIGUEZ</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4305</v>
+        <v>1.1353</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0836</v>
+        <v>1.0396</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3469</v>
+        <v>0.09569999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6211</v>
+        <v>0.2389</v>
       </c>
       <c r="H15" t="n">
-        <v>0.924</v>
+        <v>-0.7106</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.303</v>
+        <v>0.9495</v>
       </c>
       <c r="J15" t="n">
-        <v>1.422</v>
+        <v>1.0952</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3384</v>
+        <v>-0.5032</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0837</v>
+        <v>1.5984</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8008999999999999</v>
+        <v>-0.8563</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4143</v>
+        <v>-0.2074</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3866</v>
+        <v>-0.6489</v>
       </c>
       <c r="P15" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2301</v>
+        <v>0.5103</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6616</v>
+        <v>-0.0555</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5686</v>
+        <v>0.5658</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4138</v>
+        <v>0.9411</v>
       </c>
       <c r="E16" t="n">
-        <v>3.8313</v>
+        <v>2.3834</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.4175</v>
+        <v>-1.4423</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8791</v>
@@ -1702,13 +1702,13 @@
         <v>0.9654</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2929</v>
+        <v>1.8202</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7576</v>
+        <v>1.3097</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5354</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>M. SOLA IDRISU</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1452</v>
+        <v>0.8522</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2123</v>
+        <v>-1.3671</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06710000000000001</v>
+        <v>2.2193</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2389</v>
+        <v>-0.1131</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7106</v>
+        <v>2.7375</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9495</v>
+        <v>-2.8506</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0952</v>
+        <v>-0.3597</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5032</v>
+        <v>2.3937</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5984</v>
+        <v>-2.7533</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8563</v>
+        <v>0.2466</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2074</v>
+        <v>0.3439</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6489</v>
+        <v>-0.0973</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3862</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4798</v>
+        <v>1.9307</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8829</v>
+        <v>0.9234</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4031</v>
+        <v>1.0073</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SOLA IDRISU</t>
+          <t>F. DIAZ MARTINEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.218</v>
+        <v>0.834</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9876</v>
+        <v>0.835</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7697</v>
+        <v>-0.001</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1131</v>
+        <v>-1.4583</v>
       </c>
       <c r="H18" t="n">
-        <v>2.7375</v>
+        <v>2.0411</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.8506</v>
+        <v>-3.4994</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3597</v>
+        <v>0.0187</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3937</v>
+        <v>2.0419</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.7533</v>
+        <v>-2.0232</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2466</v>
+        <v>-1.477</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3439</v>
+        <v>-0.0008</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0973</v>
+        <v>-1.4763</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9654</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9654</v>
+        <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8605</v>
+        <v>2.9029</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3028</v>
+        <v>2.1992</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5577</v>
+        <v>0.7037</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8931</v>
+        <v>-0.5732</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8694</v>
+        <v>-1.6626</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.0894</v>
       </c>
       <c r="G19" t="n">
         <v>0.1991</v>
@@ -1936,13 +1936,13 @@
         <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3199</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2759</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.044</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8849</v>
+        <v>-1.525</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7523</v>
+        <v>-0.442</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1326</v>
+        <v>-1.083</v>
       </c>
       <c r="G20" t="n">
         <v>-1.8076</v>
@@ -2014,13 +2014,13 @@
         <v>0.1931</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2703</v>
+        <v>0.0896</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1655</v>
+        <v>0.1447</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1048</v>
+        <v>-0.0551</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>P. ROBLES LLANOS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.9887</v>
+        <v>-2.3541</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8433</v>
+        <v>-3.0354</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1454</v>
+        <v>0.6813</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2714</v>
+        <v>-4.9791</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6135</v>
+        <v>-3.2204</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6578000000000001</v>
+        <v>-1.7587</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2984</v>
+        <v>-3.7155</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9923999999999999</v>
+        <v>-2.8747</v>
       </c>
       <c r="L21" t="n">
-        <v>0.6941000000000001</v>
+        <v>-0.8408</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.973</v>
+        <v>-1.2637</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6211</v>
+        <v>-0.3458</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3519</v>
+        <v>-0.9179</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9654</v>
+        <v>-1.7377</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9308</v>
+        <v>-2.8962</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2481</v>
+        <v>1.9926</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3859</v>
+        <v>1.2061</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1378</v>
+        <v>0.7865</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.3701</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.3701</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. ROBLES LLANOS</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.3579</v>
+        <v>-2.6577</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.3799</v>
+        <v>-1.6364</v>
       </c>
       <c r="F22" t="n">
-        <v>0.022</v>
+        <v>-1.0213</v>
       </c>
       <c r="G22" t="n">
-        <v>-4.9791</v>
+        <v>-2.2714</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.2204</v>
+        <v>-1.6135</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.7587</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7155</v>
+        <v>-0.2984</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.8747</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8408</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2637</v>
+        <v>-1.973</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3458</v>
+        <v>-0.6211</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9179</v>
+        <v>-1.3519</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.7377</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.8962</v>
+        <v>-1.9308</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1585</v>
+        <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0112</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1384</v>
+        <v>0.5928</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1272</v>
+        <v>-0.0137</v>
       </c>
       <c r="V22" t="n">
-        <v>2.3701</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.3701</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.7732</v>
+        <v>8.152099999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>5.651300000000002</v>
+        <v>5.6513</v>
       </c>
       <c r="F23" t="n">
-        <v>1.122</v>
+        <v>2.500800000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-3.723199999999999</v>
@@ -2221,7 +2221,7 @@
         <v>-8.8956</v>
       </c>
       <c r="J23" t="n">
-        <v>4.5634</v>
+        <v>4.563400000000001</v>
       </c>
       <c r="K23" t="n">
         <v>6.213299999999999</v>
@@ -2230,13 +2230,13 @@
         <v>-1.6496</v>
       </c>
       <c r="M23" t="n">
-        <v>-8.286899999999999</v>
+        <v>-8.286900000000001</v>
       </c>
       <c r="N23" t="n">
         <v>-1.041</v>
       </c>
       <c r="O23" t="n">
-        <v>-7.246000000000001</v>
+        <v>-7.246</v>
       </c>
       <c r="P23" t="n">
         <v>-4.827</v>
@@ -2248,13 +2248,13 @@
         <v>7.7232</v>
       </c>
       <c r="S23" t="n">
-        <v>13.6525</v>
+        <v>15.0315</v>
       </c>
       <c r="T23" t="n">
-        <v>9.5115</v>
+        <v>9.511699999999999</v>
       </c>
       <c r="U23" t="n">
-        <v>4.1412</v>
+        <v>5.5199</v>
       </c>
       <c r="V23" t="n">
         <v>1.671</v>
